--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>79699</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135742998</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135743002</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135743005</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135743006</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135743007</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79699</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135742998</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135743002</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135743005</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135743006</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135743007</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135742998</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135743002</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135743005</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135743006</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135743007</v>
       </c>
       <c r="B19" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79705</v>
+        <v>79706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135742998</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135743002</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135743005</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135743006</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135743007</v>
       </c>
       <c r="B19" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61485-2025 artfynd.xlsx
+++ b/artfynd/A 61485-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743011</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743003</v>
       </c>
       <c r="B3" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743008</v>
       </c>
       <c r="B4" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743012</v>
       </c>
       <c r="B5" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135742997</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743000</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743014</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743015</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135742996</v>
       </c>
       <c r="B10" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743001</v>
       </c>
       <c r="B11" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743004</v>
       </c>
       <c r="B12" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135743013</v>
       </c>
       <c r="B13" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135743009</v>
       </c>
       <c r="B14" t="n">
-        <v>79710</v>
+        <v>79716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135742998</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135743002</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135743005</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135743006</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135743007</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135742999</v>
       </c>
       <c r="B20" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
